--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO TOLEDO BASKET.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO TOLEDO BASKET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>L. GARCIA MUNOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,67 +787,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4978</v>
+        <v>4.2731</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4978</v>
+        <v>3.1698</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.1032</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4978</v>
+        <v>-2.3266</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4601</v>
+        <v>3.8963</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0375</v>
+        <v>-6.223100000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4978</v>
+        <v>3.0085</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4601</v>
+        <v>4.2651</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0375</v>
+        <v>-1.2564</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-5.3352</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3687000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-4.9667</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3147</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.0947</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>7.4094</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.3225</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1446</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1779</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.9627</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.111499999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1487</v>
       </c>
     </row>
     <row r="6">
@@ -1009,7 +1009,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA MUNOZ</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1018,76 +1018,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2248</v>
+        <v>-1.4512</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3279</v>
+        <v>-0.5183000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1032</v>
+        <v>-0.9329</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.8245</v>
+        <v>-5.0327</v>
       </c>
       <c r="H8" t="n">
-        <v>1.436</v>
+        <v>-0.8606</v>
       </c>
       <c r="I8" t="n">
-        <v>-9.2608</v>
+        <v>-4.1721</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4893</v>
+        <v>-2.6019</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8048</v>
+        <v>-1.119</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.2941</v>
+        <v>-1.483</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.3352</v>
+        <v>-2.4307</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3687000000000001</v>
+        <v>0.2584</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.9667</v>
+        <v>-2.6891</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3147</v>
+        <v>2.1449</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0947</v>
+        <v>-0.9749</v>
       </c>
       <c r="R8" t="n">
-        <v>7.4094</v>
+        <v>3.1198</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3225</v>
+        <v>0.548</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1446</v>
+        <v>0.3928</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1779</v>
+        <v>0.1552</v>
       </c>
       <c r="V8" t="n">
-        <v>2.9627</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>4.111499999999999</v>
+        <v>2.6657</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1487</v>
+        <v>-1.7772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4512</v>
+        <v>-3.250300000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5183000000000001</v>
+        <v>2.2776</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9329</v>
+        <v>-5.5278</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0327</v>
+        <v>-3.5806</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8606</v>
+        <v>1.4618</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1721</v>
+        <v>-5.0425</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6019</v>
+        <v>0.3114999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.119</v>
+        <v>-0.01119999999999997</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.483</v>
+        <v>0.3227</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4307</v>
+        <v>-3.8921</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2584</v>
+        <v>1.473</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.6891</v>
+        <v>-5.3651</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1449</v>
+        <v>2.5349</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9749</v>
+        <v>-4.0948</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1198</v>
+        <v>6.6295</v>
       </c>
       <c r="S9" t="n">
-        <v>0.548</v>
+        <v>2.2751</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3928</v>
+        <v>1.512</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1552</v>
+        <v>0.7631</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8885999999999999</v>
+        <v>-4.4796</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6657</v>
+        <v>4.5488</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7772</v>
+        <v>-9.0284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.250300000000001</v>
+        <v>-4.803000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2776</v>
+        <v>-1.5951</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5278</v>
+        <v>-3.2079</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5806</v>
+        <v>-2.4705</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4618</v>
+        <v>2.6402</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.0425</v>
+        <v>-5.110799999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3114999999999998</v>
+        <v>4.6818</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01119999999999997</v>
+        <v>2.8108</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3227</v>
+        <v>1.871</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8921</v>
+        <v>-7.1523</v>
       </c>
       <c r="N10" t="n">
-        <v>1.473</v>
+        <v>-0.1706000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.3651</v>
+        <v>-6.9818</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5349</v>
+        <v>-5.849600000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0948</v>
+        <v>-13.454</v>
       </c>
       <c r="R10" t="n">
-        <v>6.6295</v>
+        <v>7.6044</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2751</v>
+        <v>1.9149</v>
       </c>
       <c r="T10" t="n">
-        <v>1.512</v>
+        <v>1.3943</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7631</v>
+        <v>0.5206000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.4796</v>
+        <v>1.6022</v>
       </c>
       <c r="W10" t="n">
-        <v>4.5488</v>
+        <v>5.7828</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.0284</v>
+        <v>-4.1806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.803000000000001</v>
+        <v>-5.2633</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5951</v>
+        <v>-2.4663</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2079</v>
+        <v>-2.7969</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4705</v>
+        <v>-3.5424</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6402</v>
+        <v>-1.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.110799999999999</v>
+        <v>-2.4673</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6818</v>
+        <v>-1.4515</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8108</v>
+        <v>-0.455</v>
       </c>
       <c r="L11" t="n">
-        <v>1.871</v>
+        <v>-0.9964999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.1523</v>
+        <v>-2.0909</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1706000000000001</v>
+        <v>-0.6202000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.9818</v>
+        <v>-1.4708</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.849600000000001</v>
+        <v>1.7549</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.454</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.6044</v>
+        <v>1.7549</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9149</v>
+        <v>-0.8444</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3943</v>
+        <v>-0.3518000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5206000000000001</v>
+        <v>-0.4925</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6022</v>
+        <v>-2.6312</v>
       </c>
       <c r="W11" t="n">
-        <v>5.7828</v>
+        <v>-0.6629</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.1806</v>
+        <v>-1.9683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1330,76 +1330,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2633</v>
+        <v>-6.790900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4663</v>
+        <v>-4.7549</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7969</v>
+        <v>-2.0358</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5424</v>
+        <v>0.3410000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0751</v>
+        <v>8.388500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4673</v>
+        <v>-8.047499999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4515</v>
+        <v>4.7056</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.455</v>
+        <v>7.534000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9964999999999999</v>
+        <v>-2.8285</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0909</v>
+        <v>-4.3646</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6202000000000001</v>
+        <v>0.8546000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4708</v>
+        <v>-5.2189</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7549</v>
+        <v>-1.5598</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-9.359400000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7549</v>
+        <v>7.7994</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8444</v>
+        <v>-0.2198</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3518000000000001</v>
+        <v>-0.884</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4925</v>
+        <v>0.6641</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6312</v>
+        <v>-5.3521</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6629</v>
+        <v>0.7827999999999998</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9683</v>
+        <v>-6.1349</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,144 +1411,66 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.790900000000001</v>
+        <v>8.659799999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7549</v>
+        <v>14.6694</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0358</v>
+        <v>-6.009600000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3410000000000002</v>
+        <v>-8.259</v>
       </c>
       <c r="H13" t="n">
-        <v>8.388500000000001</v>
+        <v>26.9791</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.047499999999999</v>
+        <v>-35.2388</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7056</v>
+        <v>39.9518</v>
       </c>
       <c r="K13" t="n">
-        <v>7.534000000000001</v>
+        <v>28.2625</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8285</v>
+        <v>11.6892</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.3646</v>
+        <v>-48.21090000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8546000000000001</v>
+        <v>-1.283500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2189</v>
+        <v>-46.92769999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5598</v>
+        <v>15.5989</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.359400000000001</v>
+        <v>-54.5964</v>
       </c>
       <c r="R13" t="n">
-        <v>7.7994</v>
+        <v>70.19459999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2198</v>
+        <v>9.754799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.884</v>
+        <v>4.1407</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6641</v>
+        <v>5.6143</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.3521</v>
+        <v>-8.4344</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7827999999999998</v>
+        <v>25.1732</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1349</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8.659699999999997</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14.6695</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-6.009600000000001</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-8.2591</v>
-      </c>
-      <c r="H14" t="n">
-        <v>26.9789</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-35.239</v>
-      </c>
-      <c r="J14" t="n">
-        <v>39.9518</v>
-      </c>
-      <c r="K14" t="n">
-        <v>28.2623</v>
-      </c>
-      <c r="L14" t="n">
-        <v>11.689</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-48.21090000000001</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-1.283500000000001</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-46.92769999999999</v>
-      </c>
-      <c r="P14" t="n">
-        <v>15.5989</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-54.5964</v>
-      </c>
-      <c r="R14" t="n">
-        <v>70.19459999999999</v>
-      </c>
-      <c r="S14" t="n">
-        <v>9.754799999999999</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.1407</v>
-      </c>
-      <c r="U14" t="n">
-        <v>5.6143</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-8.4344</v>
-      </c>
-      <c r="W14" t="n">
-        <v>25.1732</v>
-      </c>
-      <c r="X14" t="n">
         <v>-33.6077</v>
       </c>
     </row>
